--- a/docs/test/unit/NOUS-104/観点表_usageRecorder.xlsx
+++ b/docs/test/unit/NOUS-104/観点表_usageRecorder.xlsx
@@ -2737,7 +2737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3021,13 +3021,21 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>・疑い 1：不正な形式の試行は LLM が応答しており Neurons を消費しているが、トークン・Neurons を 0 で記録している。daily_usage.neurons が実際の消費より少なくなり、日次上限の判定が甘くなる。recordAttempt は result が ok 以外のときトークン・Neurons を 0 にする。設計書 4章の recordAttempt は「addDailyUsage（calls+1、runs…、トークン、Neurons）」で ok に限っておらず、P207 のワイヤーフレームも invalid_format の失敗に Neurons 31.0 を出している。TC-UT_USG-012 は設計どおりの期待結果で書いた（実施で NG になる見込み）。TC-NOUS63_DEV-02 は 0 を期待しており、疑いと食い違う</t>
+          <t>・疑い 1：不正な形式の試行は LLM が応答しており Neurons を消費しているが、トークン・Neurons を 0 で記録している。daily_usage.neurons が実際の消費より少なくなり、日次上限の判定が甘くなる。recordAttempt は result が ok 以外のときトークン・Neurons を 0 にする。不正な形式の試行のトークン・Neurons は加算するのが仕様（2026-10-26 Kouhei Tajima の決定）。TC-UT_USG-012 は仕様の期待結果で書いた（実施で NG の見込み）。TC-NOUS63_DEV-02 は 0 を期待しており、仕様と食い違う</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>・分岐 B7 の偽（6 通りのどれにも当たらない）は通せない。引数の型が ActionKind | 'none' の 6 値で、switch がすべてを返すため、型の上では到達しない（default が無いので、型を外した値なら undefined を返す）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
